--- a/data/trans_orig/IP18A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110057</t>
+          <t>110363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123615</t>
+          <t>123373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237585</t>
+          <t>237187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243232</t>
+          <t>243111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175791</t>
+          <t>176483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341837</t>
+          <t>342304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131368</t>
+          <t>131237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255482</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186158</t>
+          <t>186021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191841</t>
+          <t>191832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176407</t>
+          <t>176421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365279</t>
+          <t>364949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372441</t>
+          <t>372369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589231</t>
+          <t>588920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>595987</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>615442</t>
+          <t>615496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622634</t>
+          <t>622842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1208191</t>
+          <t>1207998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1217666</t>
+          <t>1217490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125403</t>
+          <t>124912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136411</t>
+          <t>136724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265224</t>
+          <t>264592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272335</t>
+          <t>272349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186087</t>
+          <t>186710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199604</t>
+          <t>199551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388325</t>
+          <t>388628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394922</t>
+          <t>394921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136361</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151593</t>
+          <t>152219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291771</t>
+          <t>291708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297007</t>
+          <t>297004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196910</t>
+          <t>196880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196075</t>
+          <t>195953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395641</t>
+          <t>395352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402201</t>
+          <t>402165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>653426</t>
+          <t>653253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>661605</t>
+          <t>661085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>692943</t>
+          <t>692947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702690</t>
+          <t>702844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1350603</t>
+          <t>1349887</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362056</t>
+          <t>1362207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>116649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132380</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251130</t>
+          <t>250149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187317</t>
+          <t>186750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192201</t>
+          <t>192157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203171</t>
+          <t>203115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>208055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392693</t>
+          <t>391483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399625</t>
+          <t>399441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130884</t>
+          <t>130802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135400</t>
+          <t>135398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132454</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141102</t>
+          <t>141106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265878</t>
+          <t>265859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275845</t>
+          <t>276054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184354</t>
+          <t>183518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176310</t>
+          <t>175875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363159</t>
+          <t>363264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369827</t>
+          <t>369832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>627562</t>
+          <t>627299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636592</t>
+          <t>636653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653510</t>
+          <t>653672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664151</t>
+          <t>664668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284552</t>
+          <t>1284980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1298611</t>
+          <t>1299068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70522</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77983</t>
+          <t>77878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48499</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56653</t>
+          <t>56658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53816</t>
+          <t>53729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>99164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129359</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216887</t>
+          <t>217059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227523</t>
+          <t>227611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5624</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128036</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>123237</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>113507</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>110363</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>110424</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>114834</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>128036</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>123373</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>354</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237187</t>
+          <t>237079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243111</t>
+          <t>243235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>114834</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>114834</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>114834</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,107 +1066,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>179231</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>176881</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>179231</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>176483</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>538</t>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342304</t>
+          <t>341058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2433</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133313</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131363</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>133313</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131237</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>413</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255950</t>
+          <t>255960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4785</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2376</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6491</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4885</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>179911</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176521</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>190167</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>186021</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>191832</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>186052</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>191831</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>179911</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>176421</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>515</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364949</t>
+          <t>365322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372369</t>
+          <t>372433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8387</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>620489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>615304</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>622628</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>886</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>593603</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>588920</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>595978</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>588639</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>595872</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>620489</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>615496</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>622842</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1207998</t>
+          <t>1208107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1217490</t>
+          <t>1217554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8677</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>736</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4173</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8631</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>136678</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143396</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128362</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124912</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125332</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>129098</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>141182</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>136724</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143949</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>366</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264592</t>
+          <t>265102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272349</t>
+          <t>272330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145355</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4317</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5073</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3131,69 +3131,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>203164</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>199652</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>189626</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186710</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>186225</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>191027</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>203164</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>199551</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>586</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388628</t>
+          <t>388821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394921</t>
+          <t>394869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3244,52 +3244,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>191027</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>191027</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>191027</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3643</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1917</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5152</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154921</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151952</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>140146</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>136911</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141453</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136920</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141454</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154921</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152219</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291708</t>
+          <t>291132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297004</t>
+          <t>297005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,102 +3704,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5420</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1559</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4728</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1570</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5430</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7848</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7639</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3812,107 +3812,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199813</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195963</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201383</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200049</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196880</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>196615</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>201608</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199813</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>195953</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201383</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>399862</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>395143</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>402172</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>399862</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>395352</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>402165</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201383</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201383</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201383</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>201608</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>201608</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>201608</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201383</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201383</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201383</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10542</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10814</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>699079</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>693722</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>702831</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>947</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>658183</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>653253</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661085</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>652981</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>661164</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>699079</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>692947</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>702844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349887</t>
+          <t>1350060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362207</t>
+          <t>1362439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1764</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6172</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>134687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>132059</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>121057</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>116649</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>116326</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>134687</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>131934</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>346</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250149</t>
+          <t>251460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257558</t>
+          <t>257560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,74 +4960,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2983</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6568</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5615</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>206658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203163</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>208060</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>190335</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186750</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192157</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>186753</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>192168</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>206658</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>203115</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>208055</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391483</t>
+          <t>392479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399441</t>
+          <t>399670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1903</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11270</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138088</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132566</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141215</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>134097</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130802</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135398</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>130569</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>135403</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138088</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132003</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141106</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>432</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265859</t>
+          <t>266632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276054</t>
+          <t>275830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6464</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180724</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>177285</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>187433</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>183518</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>184307</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>180724</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>175875</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>509</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363264</t>
+          <t>363986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369832</t>
+          <t>369837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16503</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13046</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>660157</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>653178</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664606</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>632923</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>627299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>636653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>626381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>636206</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>660157</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>653672</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664668</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284980</t>
+          <t>1285204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299068</t>
+          <t>1299136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3779</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15902</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13140</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16098</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13839</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17144</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21666</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>33314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6997</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>870</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7942</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42305</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38396</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44447</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26949</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>46535</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>41794</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48866</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>116</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75510</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>64412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77878</t>
+          <t>71294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7305</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27758</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23606</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29872</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25032</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22275</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18995</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23718</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,09%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24375</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>44800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -7711,69 +7711,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27223</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25218</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27701</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28510</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>82</t>
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>53326</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2435</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12689</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>116209</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109033</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119287</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>97418</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93669</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>99164</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125876</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>88494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>208978</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217059</t>
+          <t>202464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227611</t>
+          <t>212727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
